--- a/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260917.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260917.xlsx
@@ -733,17 +733,17 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>84,166,452</t>
+          <t>155,214,539</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -755,17 +755,17 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>170,305,243</t>
+          <t>84,166,452</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -777,17 +777,17 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>155,214,539</t>
+          <t>170,305,243</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>大成鋼</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>107,143,315</t>
+          <t>22,378,317</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>大成鋼</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>22,378,317</t>
+          <t>107,143,315</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
